--- a/app/excel_templates/classrooms_template.xlsx
+++ b/app/excel_templates/classrooms_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Кабинеты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабинеты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
@@ -471,7 +471,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Вместимость</t>
+          <t>Вместимость классов</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2</v>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>1</v>
